--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573917947</v>
+        <v>46157.93115337808</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93115337808</v>
+        <v>46157.93181804304</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93181804304</v>
+        <v>46157.93405201376</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405201376</v>
+        <v>46157.93723276884</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723276884</v>
+        <v>46158.28221101986</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221101986</v>
+        <v>46158.29700994489</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29700994489</v>
+        <v>46158.2982077756</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2982077756</v>
+        <v>46158.33392129999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392129999</v>
+        <v>46158.36861906002</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861906002</v>
+        <v>46158.37292574889</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
